--- a/data/trans_bre/IP16B98-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16B98-Clase-trans_bre.xlsx
@@ -606,17 +606,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>-75,33; 0,0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>-100,0; 0,0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 0,0</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,33; 0,0</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 38,67</t>
+          <t>-21,42; 41,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,75</t>
+          <t>0,0; 53,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,06; 66,34</t>
+          <t>-23,21; 73,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 103,03</t>
+          <t>0,0; 114,93</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 16,18</t>
+          <t>-13,72; 16,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 18,78</t>
+          <t>-2,71; 18,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 20,35</t>
+          <t>-14,47; 19,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 23,13</t>
+          <t>-2,71; 22,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B98-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16B98-Clase-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-75,33; 0,0</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-75,33; 0,0</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,42; 41,04</t>
+          <t>-19,75; 37,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,5</t>
+          <t>0,0; 56,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 73,48</t>
+          <t>-22,59; 63,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 114,93</t>
+          <t>0,0; 131,62</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 16,31</t>
+          <t>-12,05; 16,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 18,61</t>
+          <t>-4,2; 18,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 19,86</t>
+          <t>-12,51; 20,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 22,87</t>
+          <t>-4,39; 23,24</t>
         </is>
       </c>
     </row>
